--- a/artfynd/A 63654-2023 artfynd.xlsx
+++ b/artfynd/A 63654-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63654-2023 artfynd.xlsx
+++ b/artfynd/A 63654-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>67734258</v>
       </c>
       <c r="B2" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505502.8758866379</v>
+        <v>505503</v>
       </c>
       <c r="R2" t="n">
-        <v>6704329.153846732</v>
+        <v>6704329</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2017-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,16 +779,11 @@
         <v>67734254</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505477.1184690682</v>
+        <v>505477</v>
       </c>
       <c r="R3" t="n">
-        <v>6704379.898726397</v>
+        <v>6704380</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +844,9 @@
           <t>2017-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67734257</v>
+        <v>67734256</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505492.9613328957</v>
+        <v>505482</v>
       </c>
       <c r="R4" t="n">
-        <v>6704353.791277183</v>
+        <v>6704338</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,19 +945,9 @@
           <t>2017-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,19 +978,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67734256</v>
+        <v>67734257</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505482.1204403039</v>
+        <v>505493</v>
       </c>
       <c r="R5" t="n">
-        <v>6704337.997270028</v>
+        <v>6704354</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,19 +1046,9 @@
           <t>2017-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 63654-2023 artfynd.xlsx
+++ b/artfynd/A 63654-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67734258</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67734254</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67734256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67734257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>